--- a/Online Assessment 0/web_resources/Data files for Assessments/Online Assessment 0/Data3_17.xlsx
+++ b/Online Assessment 0/web_resources/Data files for Assessments/Online Assessment 0/Data3_17.xlsx
@@ -351,7 +351,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C51"/>
+  <dimension ref="A1:C201"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -362,12 +362,12 @@
       </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
-          <t>Treatment</t>
+          <t>SelfConfidenceRating</t>
         </is>
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
-          <t>RiskTaking</t>
+          <t>Anxiety</t>
         </is>
       </c>
     </row>
@@ -378,10 +378,10 @@
         </is>
       </c>
       <c r="B2">
-        <v>-0.4117331288375524</v>
+        <v>1.025229620765268</v>
       </c>
       <c r="C2">
-        <v>0.7120787206519001</v>
+        <v>0.3009321577218054</v>
       </c>
     </row>
     <row r="3">
@@ -391,10 +391,10 @@
         </is>
       </c>
       <c r="B3">
-        <v>0.2556838268020966</v>
+        <v>1.055763855469046</v>
       </c>
       <c r="C3">
-        <v>-0.07719387532445388</v>
+        <v>-0.5583501615006479</v>
       </c>
     </row>
     <row r="4">
@@ -404,10 +404,10 @@
         </is>
       </c>
       <c r="B4">
-        <v>-0.005083633460335953</v>
+        <v>-1.432307848165029</v>
       </c>
       <c r="C4">
-        <v>-0.07716260160931958</v>
+        <v>0.7860147798217434</v>
       </c>
     </row>
     <row r="5">
@@ -417,10 +417,10 @@
         </is>
       </c>
       <c r="B5">
-        <v>-0.2845930239548136</v>
+        <v>-1.35030025352536</v>
       </c>
       <c r="C5">
-        <v>0.5126603944565776</v>
+        <v>1.240631617192431</v>
       </c>
     </row>
     <row r="6">
@@ -430,10 +430,10 @@
         </is>
       </c>
       <c r="B6">
-        <v>-0.3610190903058647</v>
+        <v>-0.07632105151945577</v>
       </c>
       <c r="C6">
-        <v>1.864642168972283</v>
+        <v>-0.1663766729914621</v>
       </c>
     </row>
     <row r="7">
@@ -443,10 +443,10 @@
         </is>
       </c>
       <c r="B7">
-        <v>0.6171777314299441</v>
+        <v>0.5169024492507134</v>
       </c>
       <c r="C7">
-        <v>-1.02201371300695</v>
+        <v>0.1035235005809111</v>
       </c>
     </row>
     <row r="8">
@@ -456,10 +456,10 @@
         </is>
       </c>
       <c r="B8">
-        <v>-0.3691338170308345</v>
+        <v>-0.6893509471069227</v>
       </c>
       <c r="C8">
-        <v>-0.4461230294237905</v>
+        <v>1.335032596073956</v>
       </c>
     </row>
     <row r="9">
@@ -469,10 +469,10 @@
         </is>
       </c>
       <c r="B9">
-        <v>-0.521104300220752</v>
+        <v>0.6304634650918758</v>
       </c>
       <c r="C9">
-        <v>-0.1071747428773379</v>
+        <v>-1.486650857816557</v>
       </c>
     </row>
     <row r="10">
@@ -482,10 +482,10 @@
         </is>
       </c>
       <c r="B10">
-        <v>-0.2533250097524374</v>
+        <v>0.1901985899698128</v>
       </c>
       <c r="C10">
-        <v>0.8084536005302694</v>
+        <v>-1.047564349757096</v>
       </c>
     </row>
     <row r="11">
@@ -495,10 +495,10 @@
         </is>
       </c>
       <c r="B11">
-        <v>-2.572874391214226</v>
+        <v>-0.7226297201032715</v>
       </c>
       <c r="C11">
-        <v>0.1767720821919641</v>
+        <v>-0.7653102916783177</v>
       </c>
     </row>
     <row r="12">
@@ -508,10 +508,10 @@
         </is>
       </c>
       <c r="B12">
-        <v>0.5975537508088538</v>
+        <v>1.154769626137382</v>
       </c>
       <c r="C12">
-        <v>-0.1348170511041067</v>
+        <v>0.317488707367286</v>
       </c>
     </row>
     <row r="13">
@@ -521,10 +521,10 @@
         </is>
       </c>
       <c r="B13">
-        <v>0.553608245344629</v>
+        <v>-0.08924890737236088</v>
       </c>
       <c r="C13">
-        <v>1.016388407827569</v>
+        <v>1.450423614167689</v>
       </c>
     </row>
     <row r="14">
@@ -534,10 +534,10 @@
         </is>
       </c>
       <c r="B14">
-        <v>0.2505391039614571</v>
+        <v>-0.7720275923619205</v>
       </c>
       <c r="C14">
-        <v>-0.6993406692403785</v>
+        <v>2.101212397201356</v>
       </c>
     </row>
     <row r="15">
@@ -547,10 +547,10 @@
         </is>
       </c>
       <c r="B15">
-        <v>-0.5551183235535823</v>
+        <v>0.7318703053737281</v>
       </c>
       <c r="C15">
-        <v>0.1318765882369023</v>
+        <v>1.100412536179278</v>
       </c>
     </row>
     <row r="16">
@@ -560,10 +560,10 @@
         </is>
       </c>
       <c r="B16">
-        <v>0.6971996212911175</v>
+        <v>-0.03429824604196029</v>
       </c>
       <c r="C16">
-        <v>-0.654560126542157</v>
+        <v>0.4452326302989451</v>
       </c>
     </row>
     <row r="17">
@@ -573,10 +573,10 @@
         </is>
       </c>
       <c r="B17">
-        <v>1.497501663455467</v>
+        <v>1.497729084015466</v>
       </c>
       <c r="C17">
-        <v>0.1852343673227093</v>
+        <v>-1.731885477611416</v>
       </c>
     </row>
     <row r="18">
@@ -586,10 +586,10 @@
         </is>
       </c>
       <c r="B18">
-        <v>2.380101357737674</v>
+        <v>0.3452576973151649</v>
       </c>
       <c r="C18">
-        <v>-0.6473075617511304</v>
+        <v>0.3784807118060188</v>
       </c>
     </row>
     <row r="19">
@@ -599,10 +599,10 @@
         </is>
       </c>
       <c r="B19">
-        <v>-2.065659675632068</v>
+        <v>-0.5958535747165423</v>
       </c>
       <c r="C19">
-        <v>0.9854371427456348</v>
+        <v>0.2446950020746357</v>
       </c>
     </row>
     <row r="20">
@@ -612,10 +612,10 @@
         </is>
       </c>
       <c r="B20">
-        <v>1.914323421914931</v>
+        <v>-0.2259785618509538</v>
       </c>
       <c r="C20">
-        <v>-0.1508308396882343</v>
+        <v>-0.1629216352153376</v>
       </c>
     </row>
     <row r="21">
@@ -625,10 +625,10 @@
         </is>
       </c>
       <c r="B21">
-        <v>0.24037101407856</v>
+        <v>-0.3193402722376147</v>
       </c>
       <c r="C21">
-        <v>0.6629308723922247</v>
+        <v>0.2098556220018209</v>
       </c>
     </row>
     <row r="22">
@@ -638,10 +638,10 @@
         </is>
       </c>
       <c r="B22">
-        <v>-1.551107574160219</v>
+        <v>0.6618366852913574</v>
       </c>
       <c r="C22">
-        <v>1.539401806380432</v>
+        <v>-0.1637673907161512</v>
       </c>
     </row>
     <row r="23">
@@ -651,10 +651,10 @@
         </is>
       </c>
       <c r="B23">
-        <v>1.015419532000226</v>
+        <v>-0.04165923644422807</v>
       </c>
       <c r="C23">
-        <v>1.634508491336797</v>
+        <v>-0.1757643003503107</v>
       </c>
     </row>
     <row r="24">
@@ -664,10 +664,10 @@
         </is>
       </c>
       <c r="B24">
-        <v>0.1381775357979934</v>
+        <v>0.7681856317966528</v>
       </c>
       <c r="C24">
-        <v>-0.1983841075229727</v>
+        <v>0.7338231522363352</v>
       </c>
     </row>
     <row r="25">
@@ -677,10 +677,10 @@
         </is>
       </c>
       <c r="B25">
-        <v>0.6636387889487921</v>
+        <v>1.050866622437252</v>
       </c>
       <c r="C25">
-        <v>1.673706377001081</v>
+        <v>-0.5966305631133106</v>
       </c>
     </row>
     <row r="26">
@@ -690,10 +690,10 @@
         </is>
       </c>
       <c r="B26">
-        <v>-0.760752816560877</v>
+        <v>0.4479496995738478</v>
       </c>
       <c r="C26">
-        <v>-0.06114571964708937</v>
+        <v>-1.535640289986565</v>
       </c>
     </row>
     <row r="27">
@@ -703,10 +703,10 @@
         </is>
       </c>
       <c r="B27">
-        <v>0.1536006005408476</v>
+        <v>-0.03054156401713761</v>
       </c>
       <c r="C27">
-        <v>0.2026421562152624</v>
+        <v>0.2236093097893591</v>
       </c>
     </row>
     <row r="28">
@@ -716,10 +716,10 @@
         </is>
       </c>
       <c r="B28">
-        <v>-0.4145177123527012</v>
+        <v>0.6368681788574729</v>
       </c>
       <c r="C28">
-        <v>-0.3074874976214648</v>
+        <v>-1.309259638148863</v>
       </c>
     </row>
     <row r="29">
@@ -729,10 +729,10 @@
         </is>
       </c>
       <c r="B29">
-        <v>-0.6149659936704048</v>
+        <v>-0.4180569575228605</v>
       </c>
       <c r="C29">
-        <v>-0.1954985685797117</v>
+        <v>-0.5068657293692247</v>
       </c>
     </row>
     <row r="30">
@@ -742,10 +742,10 @@
         </is>
       </c>
       <c r="B30">
-        <v>0.8173758998627991</v>
+        <v>0.8608116886308885</v>
       </c>
       <c r="C30">
-        <v>-0.974401694487764</v>
+        <v>0.741364897750278</v>
       </c>
     </row>
     <row r="31">
@@ -755,10 +755,10 @@
         </is>
       </c>
       <c r="B31">
-        <v>0.02484839767309739</v>
+        <v>-0.06088914169102677</v>
       </c>
       <c r="C31">
-        <v>-0.2363299840114282</v>
+        <v>0.3772271605820894</v>
       </c>
     </row>
     <row r="32">
@@ -768,10 +768,10 @@
         </is>
       </c>
       <c r="B32">
-        <v>1.839623044567648</v>
+        <v>-0.1657729851137509</v>
       </c>
       <c r="C32">
-        <v>-0.07572665912935683</v>
+        <v>-1.366638290263695</v>
       </c>
     </row>
     <row r="33">
@@ -781,10 +781,10 @@
         </is>
       </c>
       <c r="B33">
-        <v>0.05605945255839461</v>
+        <v>-0.2936820256605455</v>
       </c>
       <c r="C33">
-        <v>-0.3648361978231942</v>
+        <v>0.9469985569825212</v>
       </c>
     </row>
     <row r="34">
@@ -794,10 +794,10 @@
         </is>
       </c>
       <c r="B34">
-        <v>0.4331497422855613</v>
+        <v>-0.7069603032233971</v>
       </c>
       <c r="C34">
-        <v>1.122853895499482</v>
+        <v>0.2284229518635733</v>
       </c>
     </row>
     <row r="35">
@@ -807,10 +807,10 @@
         </is>
       </c>
       <c r="B35">
-        <v>0.4594294002095856</v>
+        <v>-0.201953920740404</v>
       </c>
       <c r="C35">
-        <v>1.005040821334153</v>
+        <v>0.4360664063246623</v>
       </c>
     </row>
     <row r="36">
@@ -820,10 +820,10 @@
         </is>
       </c>
       <c r="B36">
-        <v>0.2040810058640804</v>
+        <v>-0.5985299784071683</v>
       </c>
       <c r="C36">
-        <v>-0.6895824161187611</v>
+        <v>0.5682519085813841</v>
       </c>
     </row>
     <row r="37">
@@ -833,10 +833,10 @@
         </is>
       </c>
       <c r="B37">
-        <v>0.6309327472734383</v>
+        <v>0.1089695040344269</v>
       </c>
       <c r="C37">
-        <v>1.586387630435646</v>
+        <v>-0.525688342986391</v>
       </c>
     </row>
     <row r="38">
@@ -846,10 +846,10 @@
         </is>
       </c>
       <c r="B38">
-        <v>1.104244931422911</v>
+        <v>1.893646404691766</v>
       </c>
       <c r="C38">
-        <v>1.498416421959749</v>
+        <v>-0.2857783202941115</v>
       </c>
     </row>
     <row r="39">
@@ -859,10 +859,10 @@
         </is>
       </c>
       <c r="B39">
-        <v>0.01613602192143947</v>
+        <v>-0.6873401857963396</v>
       </c>
       <c r="C39">
-        <v>-0.662272410267194</v>
+        <v>1.054830096263367</v>
       </c>
     </row>
     <row r="40">
@@ -872,10 +872,10 @@
         </is>
       </c>
       <c r="B40">
-        <v>0.8913767443797905</v>
+        <v>0.7245427198249778</v>
       </c>
       <c r="C40">
-        <v>-0.9452987344803088</v>
+        <v>-0.3495545455556063</v>
       </c>
     </row>
     <row r="41">
@@ -885,10 +885,10 @@
         </is>
       </c>
       <c r="B41">
-        <v>0.4343087952681459</v>
+        <v>-1.207392103274573</v>
       </c>
       <c r="C41">
-        <v>0.2909174864775009</v>
+        <v>0.5223676304186922</v>
       </c>
     </row>
     <row r="42">
@@ -898,10 +898,10 @@
         </is>
       </c>
       <c r="B42">
-        <v>-1.566120010882987</v>
+        <v>1.07087204634314</v>
       </c>
       <c r="C42">
-        <v>0.3090240897913479</v>
+        <v>0.09852389311981097</v>
       </c>
     </row>
     <row r="43">
@@ -911,10 +911,10 @@
         </is>
       </c>
       <c r="B43">
-        <v>0.3870598757555066</v>
+        <v>0.4298180597856367</v>
       </c>
       <c r="C43">
-        <v>-1.13689064120842</v>
+        <v>-0.2987538436927959</v>
       </c>
     </row>
     <row r="44">
@@ -924,10 +924,10 @@
         </is>
       </c>
       <c r="B44">
-        <v>-1.8331781776985</v>
+        <v>0.6177243790253054</v>
       </c>
       <c r="C44">
-        <v>0.3646808767559925</v>
+        <v>-1.219415406015915</v>
       </c>
     </row>
     <row r="45">
@@ -937,10 +937,10 @@
         </is>
       </c>
       <c r="B45">
-        <v>0.0177059320594977</v>
+        <v>-1.195570393140231</v>
       </c>
       <c r="C45">
-        <v>-0.6552944401709453</v>
+        <v>-2.087366267756495</v>
       </c>
     </row>
     <row r="46">
@@ -950,10 +950,10 @@
         </is>
       </c>
       <c r="B46">
-        <v>0.4157160128994288</v>
+        <v>0.7100248680895803</v>
       </c>
       <c r="C46">
-        <v>-0.190928732673938</v>
+        <v>-0.4821682888388976</v>
       </c>
     </row>
     <row r="47">
@@ -963,10 +963,10 @@
         </is>
       </c>
       <c r="B47">
-        <v>1.354936996156883</v>
+        <v>1.506056252930421</v>
       </c>
       <c r="C47">
-        <v>-1.115433665656471</v>
+        <v>-0.791793979574084</v>
       </c>
     </row>
     <row r="48">
@@ -976,10 +976,10 @@
         </is>
       </c>
       <c r="B48">
-        <v>-0.1664008507843192</v>
+        <v>-0.7394290142034371</v>
       </c>
       <c r="C48">
-        <v>-1.505469966849816</v>
+        <v>-0.4473278048733436</v>
       </c>
     </row>
     <row r="49">
@@ -989,10 +989,10 @@
         </is>
       </c>
       <c r="B49">
-        <v>-0.6525334843220443</v>
+        <v>0.05106488426743189</v>
       </c>
       <c r="C49">
-        <v>0.03324055322867547</v>
+        <v>1.18274956201085</v>
       </c>
     </row>
     <row r="50">
@@ -1002,10 +1002,10 @@
         </is>
       </c>
       <c r="B50">
-        <v>-0.7170835023072797</v>
+        <v>2.17011815475671</v>
       </c>
       <c r="C50">
-        <v>0.346831213010693</v>
+        <v>-0.8041281549989188</v>
       </c>
     </row>
     <row r="51">
@@ -1015,10 +1015,1960 @@
         </is>
       </c>
       <c r="B51">
-        <v>-0.5423330148056139</v>
+        <v>-0.8563317249393846</v>
       </c>
       <c r="C51">
-        <v>0.3055345791554103</v>
+        <v>-0.3824705261301596</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>51</t>
+        </is>
+      </c>
+      <c r="B52">
+        <v>-0.4766171956075961</v>
+      </c>
+      <c r="C52">
+        <v>0.6031445240728478</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>52</t>
+        </is>
+      </c>
+      <c r="B53">
+        <v>2.425288996883538</v>
+      </c>
+      <c r="C53">
+        <v>-0.5390226845424084</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>53</t>
+        </is>
+      </c>
+      <c r="B54">
+        <v>-0.001787110325785692</v>
+      </c>
+      <c r="C54">
+        <v>-0.8005588298089913</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>54</t>
+        </is>
+      </c>
+      <c r="B55">
+        <v>0.4985615766157472</v>
+      </c>
+      <c r="C55">
+        <v>1.236254987318206</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>55</t>
+        </is>
+      </c>
+      <c r="B56">
+        <v>-1.76536538082426</v>
+      </c>
+      <c r="C56">
+        <v>1.446736891247151</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>56</t>
+        </is>
+      </c>
+      <c r="B57">
+        <v>1.375079652532972</v>
+      </c>
+      <c r="C57">
+        <v>-1.333818712168345</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>57</t>
+        </is>
+      </c>
+      <c r="B58">
+        <v>-0.5483626671867436</v>
+      </c>
+      <c r="C58">
+        <v>0.3841626981266537</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>58</t>
+        </is>
+      </c>
+      <c r="B59">
+        <v>0.1637757215625242</v>
+      </c>
+      <c r="C59">
+        <v>0.7175970302805118</v>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>59</t>
+        </is>
+      </c>
+      <c r="B60">
+        <v>-0.1501027083917671</v>
+      </c>
+      <c r="C60">
+        <v>1.091982096452783</v>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>60</t>
+        </is>
+      </c>
+      <c r="B61">
+        <v>0.0719995845617183</v>
+      </c>
+      <c r="C61">
+        <v>1.656035146968199</v>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>61</t>
+        </is>
+      </c>
+      <c r="B62">
+        <v>-0.9678073420969214</v>
+      </c>
+      <c r="C62">
+        <v>2.810270451259926</v>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>62</t>
+        </is>
+      </c>
+      <c r="B63">
+        <v>-0.6048288302599294</v>
+      </c>
+      <c r="C63">
+        <v>0.3175807176624338</v>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>63</t>
+        </is>
+      </c>
+      <c r="B64">
+        <v>-0.6680107121019744</v>
+      </c>
+      <c r="C64">
+        <v>0.04231230701795202</v>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>64</t>
+        </is>
+      </c>
+      <c r="B65">
+        <v>-0.5910281817690702</v>
+      </c>
+      <c r="C65">
+        <v>-0.254556060414869</v>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>65</t>
+        </is>
+      </c>
+      <c r="B66">
+        <v>-0.3375636868060469</v>
+      </c>
+      <c r="C66">
+        <v>-0.9007669713115632</v>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>66</t>
+        </is>
+      </c>
+      <c r="B67">
+        <v>1.299693790712823</v>
+      </c>
+      <c r="C67">
+        <v>0.02763421953202816</v>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>67</t>
+        </is>
+      </c>
+      <c r="B68">
+        <v>-1.338294866274834</v>
+      </c>
+      <c r="C68">
+        <v>0.1977405731053289</v>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>68</t>
+        </is>
+      </c>
+      <c r="B69">
+        <v>0.3190206267461716</v>
+      </c>
+      <c r="C69">
+        <v>-1.142961945114889</v>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="inlineStr">
+        <is>
+          <t>69</t>
+        </is>
+      </c>
+      <c r="B70">
+        <v>0.5358024495218422</v>
+      </c>
+      <c r="C70">
+        <v>-0.6239190697800604</v>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="inlineStr">
+        <is>
+          <t>70</t>
+        </is>
+      </c>
+      <c r="B71">
+        <v>-1.735727330691176</v>
+      </c>
+      <c r="C71">
+        <v>0.7584984197732079</v>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="inlineStr">
+        <is>
+          <t>71</t>
+        </is>
+      </c>
+      <c r="B72">
+        <v>1.962825563730014</v>
+      </c>
+      <c r="C72">
+        <v>1.564037453330039</v>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="inlineStr">
+        <is>
+          <t>72</t>
+        </is>
+      </c>
+      <c r="B73">
+        <v>-1.717909250766334</v>
+      </c>
+      <c r="C73">
+        <v>0.7153735243659353</v>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="inlineStr">
+        <is>
+          <t>73</t>
+        </is>
+      </c>
+      <c r="B74">
+        <v>1.079514213979515</v>
+      </c>
+      <c r="C74">
+        <v>-0.3731196141652051</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>74</t>
+        </is>
+      </c>
+      <c r="B75">
+        <v>0.9607293435534175</v>
+      </c>
+      <c r="C75">
+        <v>-1.231138888869054</v>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="inlineStr">
+        <is>
+          <t>75</t>
+        </is>
+      </c>
+      <c r="B76">
+        <v>-0.7936940011658166</v>
+      </c>
+      <c r="C76">
+        <v>-0.5294757543976593</v>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="inlineStr">
+        <is>
+          <t>76</t>
+        </is>
+      </c>
+      <c r="B77">
+        <v>-0.5885729025525298</v>
+      </c>
+      <c r="C77">
+        <v>0.853699195541731</v>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="inlineStr">
+        <is>
+          <t>77</t>
+        </is>
+      </c>
+      <c r="B78">
+        <v>0.05627177255580858</v>
+      </c>
+      <c r="C78">
+        <v>-0.4928751102710429</v>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="inlineStr">
+        <is>
+          <t>78</t>
+        </is>
+      </c>
+      <c r="B79">
+        <v>1.530887172214782</v>
+      </c>
+      <c r="C79">
+        <v>0.2348926917896204</v>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="inlineStr">
+        <is>
+          <t>79</t>
+        </is>
+      </c>
+      <c r="B80">
+        <v>-1.269859116245739</v>
+      </c>
+      <c r="C80">
+        <v>0.5380303327932332</v>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="inlineStr">
+        <is>
+          <t>80</t>
+        </is>
+      </c>
+      <c r="B81">
+        <v>-0.424729590809091</v>
+      </c>
+      <c r="C81">
+        <v>1.088385590414451</v>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="inlineStr">
+        <is>
+          <t>81</t>
+        </is>
+      </c>
+      <c r="B82">
+        <v>-0.1609764576446022</v>
+      </c>
+      <c r="C82">
+        <v>0.1855402936101864</v>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="inlineStr">
+        <is>
+          <t>82</t>
+        </is>
+      </c>
+      <c r="B83">
+        <v>-1.096825789476416</v>
+      </c>
+      <c r="C83">
+        <v>-0.3074725589421861</v>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="inlineStr">
+        <is>
+          <t>83</t>
+        </is>
+      </c>
+      <c r="B84">
+        <v>-0.2240866873696309</v>
+      </c>
+      <c r="C84">
+        <v>-0.3086023059445872</v>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="inlineStr">
+        <is>
+          <t>84</t>
+        </is>
+      </c>
+      <c r="B85">
+        <v>-0.1127729748370824</v>
+      </c>
+      <c r="C85">
+        <v>-0.06492710079293598</v>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="inlineStr">
+        <is>
+          <t>85</t>
+        </is>
+      </c>
+      <c r="B86">
+        <v>-1.541089676818848</v>
+      </c>
+      <c r="C86">
+        <v>0.6395673888880815</v>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="inlineStr">
+        <is>
+          <t>86</t>
+        </is>
+      </c>
+      <c r="B87">
+        <v>-0.5434687687196528</v>
+      </c>
+      <c r="C87">
+        <v>0.7214561466416463</v>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" t="inlineStr">
+        <is>
+          <t>87</t>
+        </is>
+      </c>
+      <c r="B88">
+        <v>1.219793510962657</v>
+      </c>
+      <c r="C88">
+        <v>-0.001263049330073818</v>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" t="inlineStr">
+        <is>
+          <t>88</t>
+        </is>
+      </c>
+      <c r="B89">
+        <v>-0.1027620885544549</v>
+      </c>
+      <c r="C89">
+        <v>0.5485759687868157</v>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" t="inlineStr">
+        <is>
+          <t>89</t>
+        </is>
+      </c>
+      <c r="B90">
+        <v>-0.6558084731238917</v>
+      </c>
+      <c r="C90">
+        <v>0.9443132361297583</v>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" t="inlineStr">
+        <is>
+          <t>90</t>
+        </is>
+      </c>
+      <c r="B91">
+        <v>-0.9287849514491006</v>
+      </c>
+      <c r="C91">
+        <v>-0.06306039596157614</v>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" t="inlineStr">
+        <is>
+          <t>91</t>
+        </is>
+      </c>
+      <c r="B92">
+        <v>0.4353078281972049</v>
+      </c>
+      <c r="C92">
+        <v>0.643842129392332</v>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" t="inlineStr">
+        <is>
+          <t>92</t>
+        </is>
+      </c>
+      <c r="B93">
+        <v>-0.843726231728849</v>
+      </c>
+      <c r="C93">
+        <v>1.581055620032654</v>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" t="inlineStr">
+        <is>
+          <t>93</t>
+        </is>
+      </c>
+      <c r="B94">
+        <v>1.074277711702421</v>
+      </c>
+      <c r="C94">
+        <v>-1.231718952296445</v>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" t="inlineStr">
+        <is>
+          <t>94</t>
+        </is>
+      </c>
+      <c r="B95">
+        <v>-1.999545177688934</v>
+      </c>
+      <c r="C95">
+        <v>-0.258144028169909</v>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" t="inlineStr">
+        <is>
+          <t>95</t>
+        </is>
+      </c>
+      <c r="B96">
+        <v>0.8320700534608709</v>
+      </c>
+      <c r="C96">
+        <v>-0.6100997594447555</v>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" t="inlineStr">
+        <is>
+          <t>96</t>
+        </is>
+      </c>
+      <c r="B97">
+        <v>-1.057797177718273</v>
+      </c>
+      <c r="C97">
+        <v>0.0122873790939636</v>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" t="inlineStr">
+        <is>
+          <t>97</t>
+        </is>
+      </c>
+      <c r="B98">
+        <v>-2.027592445103189</v>
+      </c>
+      <c r="C98">
+        <v>2.553966192746048</v>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" t="inlineStr">
+        <is>
+          <t>98</t>
+        </is>
+      </c>
+      <c r="B99">
+        <v>-0.08618012499183014</v>
+      </c>
+      <c r="C99">
+        <v>-0.09418524298367564</v>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" t="inlineStr">
+        <is>
+          <t>99</t>
+        </is>
+      </c>
+      <c r="B100">
+        <v>-1.150237210983216</v>
+      </c>
+      <c r="C100">
+        <v>0.1378982726267158</v>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="B101">
+        <v>0.1593497346855277</v>
+      </c>
+      <c r="C101">
+        <v>0.4596484561026744</v>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" t="inlineStr">
+        <is>
+          <t>101</t>
+        </is>
+      </c>
+      <c r="B102">
+        <v>-1.485035748308087</v>
+      </c>
+      <c r="C102">
+        <v>1.991354640826968</v>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" t="inlineStr">
+        <is>
+          <t>102</t>
+        </is>
+      </c>
+      <c r="B103">
+        <v>-1.968799991320853</v>
+      </c>
+      <c r="C103">
+        <v>1.963245023673866</v>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" t="inlineStr">
+        <is>
+          <t>103</t>
+        </is>
+      </c>
+      <c r="B104">
+        <v>-1.321074217700818</v>
+      </c>
+      <c r="C104">
+        <v>1.076086588679486</v>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" t="inlineStr">
+        <is>
+          <t>104</t>
+        </is>
+      </c>
+      <c r="B105">
+        <v>1.65759877313382</v>
+      </c>
+      <c r="C105">
+        <v>-1.448685182808424</v>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" t="inlineStr">
+        <is>
+          <t>105</t>
+        </is>
+      </c>
+      <c r="B106">
+        <v>-0.8163703678544162</v>
+      </c>
+      <c r="C106">
+        <v>1.417625257089735</v>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" t="inlineStr">
+        <is>
+          <t>106</t>
+        </is>
+      </c>
+      <c r="B107">
+        <v>-2.562551728652106</v>
+      </c>
+      <c r="C107">
+        <v>0.6170578049555919</v>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" t="inlineStr">
+        <is>
+          <t>107</t>
+        </is>
+      </c>
+      <c r="B108">
+        <v>-0.0634627039865974</v>
+      </c>
+      <c r="C108">
+        <v>-1.250150438723375</v>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" t="inlineStr">
+        <is>
+          <t>108</t>
+        </is>
+      </c>
+      <c r="B109">
+        <v>0.5764300196738329</v>
+      </c>
+      <c r="C109">
+        <v>-0.9218791968392348</v>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" t="inlineStr">
+        <is>
+          <t>109</t>
+        </is>
+      </c>
+      <c r="B110">
+        <v>-0.7846852156328182</v>
+      </c>
+      <c r="C110">
+        <v>-0.7039160134546145</v>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" t="inlineStr">
+        <is>
+          <t>110</t>
+        </is>
+      </c>
+      <c r="B111">
+        <v>0.5375292048426568</v>
+      </c>
+      <c r="C111">
+        <v>-2.112921568008057</v>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" t="inlineStr">
+        <is>
+          <t>111</t>
+        </is>
+      </c>
+      <c r="B112">
+        <v>0.7729738045356436</v>
+      </c>
+      <c r="C112">
+        <v>0.8205502910126843</v>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" t="inlineStr">
+        <is>
+          <t>112</t>
+        </is>
+      </c>
+      <c r="B113">
+        <v>0.6326620350049958</v>
+      </c>
+      <c r="C113">
+        <v>1.0244106154344</v>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" t="inlineStr">
+        <is>
+          <t>113</t>
+        </is>
+      </c>
+      <c r="B114">
+        <v>-1.097700223415371</v>
+      </c>
+      <c r="C114">
+        <v>0.4258446141528501</v>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" t="inlineStr">
+        <is>
+          <t>114</t>
+        </is>
+      </c>
+      <c r="B115">
+        <v>0.6227767870513996</v>
+      </c>
+      <c r="C115">
+        <v>-0.118687150292506</v>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" t="inlineStr">
+        <is>
+          <t>115</t>
+        </is>
+      </c>
+      <c r="B116">
+        <v>0.8596158976990717</v>
+      </c>
+      <c r="C116">
+        <v>-2.025639601579468</v>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" t="inlineStr">
+        <is>
+          <t>116</t>
+        </is>
+      </c>
+      <c r="B117">
+        <v>-1.352427206544941</v>
+      </c>
+      <c r="C117">
+        <v>1.166001800812872</v>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" t="inlineStr">
+        <is>
+          <t>117</t>
+        </is>
+      </c>
+      <c r="B118">
+        <v>0.2588629471996457</v>
+      </c>
+      <c r="C118">
+        <v>-0.9053000251136313</v>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" t="inlineStr">
+        <is>
+          <t>118</t>
+        </is>
+      </c>
+      <c r="B119">
+        <v>-1.09081453797649</v>
+      </c>
+      <c r="C119">
+        <v>0.373612497717205</v>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" t="inlineStr">
+        <is>
+          <t>119</t>
+        </is>
+      </c>
+      <c r="B120">
+        <v>-0.5300801808286941</v>
+      </c>
+      <c r="C120">
+        <v>1.856044271802288</v>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" t="inlineStr">
+        <is>
+          <t>120</t>
+        </is>
+      </c>
+      <c r="B121">
+        <v>-3.181787869415196</v>
+      </c>
+      <c r="C121">
+        <v>0.03807857062824516</v>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" t="inlineStr">
+        <is>
+          <t>121</t>
+        </is>
+      </c>
+      <c r="B122">
+        <v>0.1959565211500095</v>
+      </c>
+      <c r="C122">
+        <v>0.5694356502964875</v>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" t="inlineStr">
+        <is>
+          <t>122</t>
+        </is>
+      </c>
+      <c r="B123">
+        <v>0.7321180948914064</v>
+      </c>
+      <c r="C123">
+        <v>-0.6380431589115034</v>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" t="inlineStr">
+        <is>
+          <t>123</t>
+        </is>
+      </c>
+      <c r="B124">
+        <v>0.1360202696951601</v>
+      </c>
+      <c r="C124">
+        <v>-0.4009065748919089</v>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" t="inlineStr">
+        <is>
+          <t>124</t>
+        </is>
+      </c>
+      <c r="B125">
+        <v>0.4282192508195804</v>
+      </c>
+      <c r="C125">
+        <v>-1.181447155610642</v>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" t="inlineStr">
+        <is>
+          <t>125</t>
+        </is>
+      </c>
+      <c r="B126">
+        <v>1.781773933725453</v>
+      </c>
+      <c r="C126">
+        <v>0.4659677233177706</v>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" t="inlineStr">
+        <is>
+          <t>126</t>
+        </is>
+      </c>
+      <c r="B127">
+        <v>-0.2095691944697965</v>
+      </c>
+      <c r="C127">
+        <v>0.2073841742759619</v>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" t="inlineStr">
+        <is>
+          <t>127</t>
+        </is>
+      </c>
+      <c r="B128">
+        <v>-0.1159451942821323</v>
+      </c>
+      <c r="C128">
+        <v>-2.159557345678455</v>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" t="inlineStr">
+        <is>
+          <t>128</t>
+        </is>
+      </c>
+      <c r="B129">
+        <v>-1.103618818236251</v>
+      </c>
+      <c r="C129">
+        <v>0.71718392510537</v>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" t="inlineStr">
+        <is>
+          <t>129</t>
+        </is>
+      </c>
+      <c r="B130">
+        <v>-0.2448261121686709</v>
+      </c>
+      <c r="C130">
+        <v>-2.066247237019936</v>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" t="inlineStr">
+        <is>
+          <t>130</t>
+        </is>
+      </c>
+      <c r="B131">
+        <v>-2.150373871468562</v>
+      </c>
+      <c r="C131">
+        <v>2.362081834330426</v>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" t="inlineStr">
+        <is>
+          <t>131</t>
+        </is>
+      </c>
+      <c r="B132">
+        <v>-0.6183527882643248</v>
+      </c>
+      <c r="C132">
+        <v>0.9141493853585021</v>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" t="inlineStr">
+        <is>
+          <t>132</t>
+        </is>
+      </c>
+      <c r="B133">
+        <v>1.698884798678058</v>
+      </c>
+      <c r="C133">
+        <v>-2.430157238750266</v>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" t="inlineStr">
+        <is>
+          <t>133</t>
+        </is>
+      </c>
+      <c r="B134">
+        <v>-1.547448330740552</v>
+      </c>
+      <c r="C134">
+        <v>1.64071858049918</v>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" t="inlineStr">
+        <is>
+          <t>134</t>
+        </is>
+      </c>
+      <c r="B135">
+        <v>0.3250113197760665</v>
+      </c>
+      <c r="C135">
+        <v>2.802604516647159</v>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" t="inlineStr">
+        <is>
+          <t>135</t>
+        </is>
+      </c>
+      <c r="B136">
+        <v>0.7450147464441718</v>
+      </c>
+      <c r="C136">
+        <v>-2.208810726285086</v>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" t="inlineStr">
+        <is>
+          <t>136</t>
+        </is>
+      </c>
+      <c r="B137">
+        <v>-0.6661280694822928</v>
+      </c>
+      <c r="C137">
+        <v>1.330100576560113</v>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" t="inlineStr">
+        <is>
+          <t>137</t>
+        </is>
+      </c>
+      <c r="B138">
+        <v>-0.07511308468825972</v>
+      </c>
+      <c r="C138">
+        <v>-0.4392534004197458</v>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" t="inlineStr">
+        <is>
+          <t>138</t>
+        </is>
+      </c>
+      <c r="B139">
+        <v>-1.130254706195891</v>
+      </c>
+      <c r="C139">
+        <v>0.9328500954399506</v>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" t="inlineStr">
+        <is>
+          <t>139</t>
+        </is>
+      </c>
+      <c r="B140">
+        <v>0.1724485040065493</v>
+      </c>
+      <c r="C140">
+        <v>-0.1429460748246264</v>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" t="inlineStr">
+        <is>
+          <t>140</t>
+        </is>
+      </c>
+      <c r="B141">
+        <v>0.6080840945196049</v>
+      </c>
+      <c r="C141">
+        <v>-0.4106384144313476</v>
+      </c>
+    </row>
+    <row r="142">
+      <c r="A142" t="inlineStr">
+        <is>
+          <t>141</t>
+        </is>
+      </c>
+      <c r="B142">
+        <v>0.9448476842186878</v>
+      </c>
+      <c r="C142">
+        <v>-0.8550232014589106</v>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143" t="inlineStr">
+        <is>
+          <t>142</t>
+        </is>
+      </c>
+      <c r="B143">
+        <v>0.4338979827959306</v>
+      </c>
+      <c r="C143">
+        <v>1.866339725722936</v>
+      </c>
+    </row>
+    <row r="144">
+      <c r="A144" t="inlineStr">
+        <is>
+          <t>143</t>
+        </is>
+      </c>
+      <c r="B144">
+        <v>1.834020321221099</v>
+      </c>
+      <c r="C144">
+        <v>0.238206715560414</v>
+      </c>
+    </row>
+    <row r="145">
+      <c r="A145" t="inlineStr">
+        <is>
+          <t>144</t>
+        </is>
+      </c>
+      <c r="B145">
+        <v>-0.5957182219541008</v>
+      </c>
+      <c r="C145">
+        <v>0.3203182555928612</v>
+      </c>
+    </row>
+    <row r="146">
+      <c r="A146" t="inlineStr">
+        <is>
+          <t>145</t>
+        </is>
+      </c>
+      <c r="B146">
+        <v>1.342011841924622</v>
+      </c>
+      <c r="C146">
+        <v>-1.739810271154776</v>
+      </c>
+    </row>
+    <row r="147">
+      <c r="A147" t="inlineStr">
+        <is>
+          <t>146</t>
+        </is>
+      </c>
+      <c r="B147">
+        <v>0.6294277453983504</v>
+      </c>
+      <c r="C147">
+        <v>-0.5759241386584042</v>
+      </c>
+    </row>
+    <row r="148">
+      <c r="A148" t="inlineStr">
+        <is>
+          <t>147</t>
+        </is>
+      </c>
+      <c r="B148">
+        <v>0.3677271117071173</v>
+      </c>
+      <c r="C148">
+        <v>1.029908947276391</v>
+      </c>
+    </row>
+    <row r="149">
+      <c r="A149" t="inlineStr">
+        <is>
+          <t>148</t>
+        </is>
+      </c>
+      <c r="B149">
+        <v>-0.1589721548620286</v>
+      </c>
+      <c r="C149">
+        <v>1.37348056382058</v>
+      </c>
+    </row>
+    <row r="150">
+      <c r="A150" t="inlineStr">
+        <is>
+          <t>149</t>
+        </is>
+      </c>
+      <c r="B150">
+        <v>0.6649033023943762</v>
+      </c>
+      <c r="C150">
+        <v>-1.876331753096203</v>
+      </c>
+    </row>
+    <row r="151">
+      <c r="A151" t="inlineStr">
+        <is>
+          <t>150</t>
+        </is>
+      </c>
+      <c r="B151">
+        <v>0.5883875659434088</v>
+      </c>
+      <c r="C151">
+        <v>-0.4541782510318558</v>
+      </c>
+    </row>
+    <row r="152">
+      <c r="A152" t="inlineStr">
+        <is>
+          <t>151</t>
+        </is>
+      </c>
+      <c r="B152">
+        <v>-2.261574194591791</v>
+      </c>
+      <c r="C152">
+        <v>-0.5148607811054915</v>
+      </c>
+    </row>
+    <row r="153">
+      <c r="A153" t="inlineStr">
+        <is>
+          <t>152</t>
+        </is>
+      </c>
+      <c r="B153">
+        <v>-0.2892642626944927</v>
+      </c>
+      <c r="C153">
+        <v>1.207064798856278</v>
+      </c>
+    </row>
+    <row r="154">
+      <c r="A154" t="inlineStr">
+        <is>
+          <t>153</t>
+        </is>
+      </c>
+      <c r="B154">
+        <v>0.199034426643914</v>
+      </c>
+      <c r="C154">
+        <v>0.8888803276396027</v>
+      </c>
+    </row>
+    <row r="155">
+      <c r="A155" t="inlineStr">
+        <is>
+          <t>154</t>
+        </is>
+      </c>
+      <c r="B155">
+        <v>-0.7604294358245354</v>
+      </c>
+      <c r="C155">
+        <v>-0.02375663513014981</v>
+      </c>
+    </row>
+    <row r="156">
+      <c r="A156" t="inlineStr">
+        <is>
+          <t>155</t>
+        </is>
+      </c>
+      <c r="B156">
+        <v>0.5353330337069255</v>
+      </c>
+      <c r="C156">
+        <v>-1.250378614772564</v>
+      </c>
+    </row>
+    <row r="157">
+      <c r="A157" t="inlineStr">
+        <is>
+          <t>156</t>
+        </is>
+      </c>
+      <c r="B157">
+        <v>1.726764467946725</v>
+      </c>
+      <c r="C157">
+        <v>-2.055935893688838</v>
+      </c>
+    </row>
+    <row r="158">
+      <c r="A158" t="inlineStr">
+        <is>
+          <t>157</t>
+        </is>
+      </c>
+      <c r="B158">
+        <v>-1.267683072882879</v>
+      </c>
+      <c r="C158">
+        <v>0.4375775263453475</v>
+      </c>
+    </row>
+    <row r="159">
+      <c r="A159" t="inlineStr">
+        <is>
+          <t>158</t>
+        </is>
+      </c>
+      <c r="B159">
+        <v>-1.491615303637634</v>
+      </c>
+      <c r="C159">
+        <v>1.905935755480932</v>
+      </c>
+    </row>
+    <row r="160">
+      <c r="A160" t="inlineStr">
+        <is>
+          <t>159</t>
+        </is>
+      </c>
+      <c r="B160">
+        <v>-2.188545455299246</v>
+      </c>
+      <c r="C160">
+        <v>0.8441011158399269</v>
+      </c>
+    </row>
+    <row r="161">
+      <c r="A161" t="inlineStr">
+        <is>
+          <t>160</t>
+        </is>
+      </c>
+      <c r="B161">
+        <v>-0.923308299502301</v>
+      </c>
+      <c r="C161">
+        <v>0.08944002314097299</v>
+      </c>
+    </row>
+    <row r="162">
+      <c r="A162" t="inlineStr">
+        <is>
+          <t>161</t>
+        </is>
+      </c>
+      <c r="B162">
+        <v>-0.2103201415877543</v>
+      </c>
+      <c r="C162">
+        <v>-0.2527284288109607</v>
+      </c>
+    </row>
+    <row r="163">
+      <c r="A163" t="inlineStr">
+        <is>
+          <t>162</t>
+        </is>
+      </c>
+      <c r="B163">
+        <v>-0.4866147652539875</v>
+      </c>
+      <c r="C163">
+        <v>0.06100948183262783</v>
+      </c>
+    </row>
+    <row r="164">
+      <c r="A164" t="inlineStr">
+        <is>
+          <t>163</t>
+        </is>
+      </c>
+      <c r="B164">
+        <v>-1.191417523256857</v>
+      </c>
+      <c r="C164">
+        <v>1.524093019186393</v>
+      </c>
+    </row>
+    <row r="165">
+      <c r="A165" t="inlineStr">
+        <is>
+          <t>164</t>
+        </is>
+      </c>
+      <c r="B165">
+        <v>0.2226212650770241</v>
+      </c>
+      <c r="C165">
+        <v>-0.09954185907053052</v>
+      </c>
+    </row>
+    <row r="166">
+      <c r="A166" t="inlineStr">
+        <is>
+          <t>165</t>
+        </is>
+      </c>
+      <c r="B166">
+        <v>-0.842868152434865</v>
+      </c>
+      <c r="C166">
+        <v>1.041209109515028</v>
+      </c>
+    </row>
+    <row r="167">
+      <c r="A167" t="inlineStr">
+        <is>
+          <t>166</t>
+        </is>
+      </c>
+      <c r="B167">
+        <v>0.2519025507998673</v>
+      </c>
+      <c r="C167">
+        <v>-0.4388857538242465</v>
+      </c>
+    </row>
+    <row r="168">
+      <c r="A168" t="inlineStr">
+        <is>
+          <t>167</t>
+        </is>
+      </c>
+      <c r="B168">
+        <v>0.2893410816861642</v>
+      </c>
+      <c r="C168">
+        <v>0.5497248690010146</v>
+      </c>
+    </row>
+    <row r="169">
+      <c r="A169" t="inlineStr">
+        <is>
+          <t>168</t>
+        </is>
+      </c>
+      <c r="B169">
+        <v>-1.391771237982875</v>
+      </c>
+      <c r="C169">
+        <v>0.9190201428436559</v>
+      </c>
+    </row>
+    <row r="170">
+      <c r="A170" t="inlineStr">
+        <is>
+          <t>169</t>
+        </is>
+      </c>
+      <c r="B170">
+        <v>-0.9290122662779104</v>
+      </c>
+      <c r="C170">
+        <v>-0.8577280489528376</v>
+      </c>
+    </row>
+    <row r="171">
+      <c r="A171" t="inlineStr">
+        <is>
+          <t>170</t>
+        </is>
+      </c>
+      <c r="B171">
+        <v>-0.6594937568797941</v>
+      </c>
+      <c r="C171">
+        <v>0.456466062716538</v>
+      </c>
+    </row>
+    <row r="172">
+      <c r="A172" t="inlineStr">
+        <is>
+          <t>171</t>
+        </is>
+      </c>
+      <c r="B172">
+        <v>0.1631408093199898</v>
+      </c>
+      <c r="C172">
+        <v>-0.9383188839199744</v>
+      </c>
+    </row>
+    <row r="173">
+      <c r="A173" t="inlineStr">
+        <is>
+          <t>172</t>
+        </is>
+      </c>
+      <c r="B173">
+        <v>0.8450608130665112</v>
+      </c>
+      <c r="C173">
+        <v>-2.148754553842822</v>
+      </c>
+    </row>
+    <row r="174">
+      <c r="A174" t="inlineStr">
+        <is>
+          <t>173</t>
+        </is>
+      </c>
+      <c r="B174">
+        <v>0.6833383744331248</v>
+      </c>
+      <c r="C174">
+        <v>-0.8615370122020243</v>
+      </c>
+    </row>
+    <row r="175">
+      <c r="A175" t="inlineStr">
+        <is>
+          <t>174</t>
+        </is>
+      </c>
+      <c r="B175">
+        <v>-0.731027621152771</v>
+      </c>
+      <c r="C175">
+        <v>-0.06702200398063113</v>
+      </c>
+    </row>
+    <row r="176">
+      <c r="A176" t="inlineStr">
+        <is>
+          <t>175</t>
+        </is>
+      </c>
+      <c r="B176">
+        <v>-0.731926418793694</v>
+      </c>
+      <c r="C176">
+        <v>0.6426077945507753</v>
+      </c>
+    </row>
+    <row r="177">
+      <c r="A177" t="inlineStr">
+        <is>
+          <t>176</t>
+        </is>
+      </c>
+      <c r="B177">
+        <v>0.09211554429368563</v>
+      </c>
+      <c r="C177">
+        <v>0.9847463529990088</v>
+      </c>
+    </row>
+    <row r="178">
+      <c r="A178" t="inlineStr">
+        <is>
+          <t>177</t>
+        </is>
+      </c>
+      <c r="B178">
+        <v>0.7657415198648315</v>
+      </c>
+      <c r="C178">
+        <v>-0.08117468600470146</v>
+      </c>
+    </row>
+    <row r="179">
+      <c r="A179" t="inlineStr">
+        <is>
+          <t>178</t>
+        </is>
+      </c>
+      <c r="B179">
+        <v>0.4255155013114997</v>
+      </c>
+      <c r="C179">
+        <v>-0.7283069395583018</v>
+      </c>
+    </row>
+    <row r="180">
+      <c r="A180" t="inlineStr">
+        <is>
+          <t>179</t>
+        </is>
+      </c>
+      <c r="B180">
+        <v>0.8457993231135027</v>
+      </c>
+      <c r="C180">
+        <v>1.131402871289778</v>
+      </c>
+    </row>
+    <row r="181">
+      <c r="A181" t="inlineStr">
+        <is>
+          <t>180</t>
+        </is>
+      </c>
+      <c r="B181">
+        <v>1.287787668793183</v>
+      </c>
+      <c r="C181">
+        <v>-0.6829181630187496</v>
+      </c>
+    </row>
+    <row r="182">
+      <c r="A182" t="inlineStr">
+        <is>
+          <t>181</t>
+        </is>
+      </c>
+      <c r="B182">
+        <v>-0.009394451124937987</v>
+      </c>
+      <c r="C182">
+        <v>0.8897433052024414</v>
+      </c>
+    </row>
+    <row r="183">
+      <c r="A183" t="inlineStr">
+        <is>
+          <t>182</t>
+        </is>
+      </c>
+      <c r="B183">
+        <v>-0.6923788415480002</v>
+      </c>
+      <c r="C183">
+        <v>1.022675867732204</v>
+      </c>
+    </row>
+    <row r="184">
+      <c r="A184" t="inlineStr">
+        <is>
+          <t>183</t>
+        </is>
+      </c>
+      <c r="B184">
+        <v>0.4872992243709451</v>
+      </c>
+      <c r="C184">
+        <v>-0.2523291419357336</v>
+      </c>
+    </row>
+    <row r="185">
+      <c r="A185" t="inlineStr">
+        <is>
+          <t>184</t>
+        </is>
+      </c>
+      <c r="B185">
+        <v>0.2028622319107977</v>
+      </c>
+      <c r="C185">
+        <v>0.1058739123540844</v>
+      </c>
+    </row>
+    <row r="186">
+      <c r="A186" t="inlineStr">
+        <is>
+          <t>185</t>
+        </is>
+      </c>
+      <c r="B186">
+        <v>0.9315751775608021</v>
+      </c>
+      <c r="C186">
+        <v>-0.8825161670721913</v>
+      </c>
+    </row>
+    <row r="187">
+      <c r="A187" t="inlineStr">
+        <is>
+          <t>186</t>
+        </is>
+      </c>
+      <c r="B187">
+        <v>0.5564542761352025</v>
+      </c>
+      <c r="C187">
+        <v>-1.367568631618289</v>
+      </c>
+    </row>
+    <row r="188">
+      <c r="A188" t="inlineStr">
+        <is>
+          <t>187</t>
+        </is>
+      </c>
+      <c r="B188">
+        <v>-1.172346649720332</v>
+      </c>
+      <c r="C188">
+        <v>0.3529307931052085</v>
+      </c>
+    </row>
+    <row r="189">
+      <c r="A189" t="inlineStr">
+        <is>
+          <t>188</t>
+        </is>
+      </c>
+      <c r="B189">
+        <v>-1.103120327034589</v>
+      </c>
+      <c r="C189">
+        <v>0.05476138579313539</v>
+      </c>
+    </row>
+    <row r="190">
+      <c r="A190" t="inlineStr">
+        <is>
+          <t>189</t>
+        </is>
+      </c>
+      <c r="B190">
+        <v>0.6983390263527661</v>
+      </c>
+      <c r="C190">
+        <v>-0.9649101479765231</v>
+      </c>
+    </row>
+    <row r="191">
+      <c r="A191" t="inlineStr">
+        <is>
+          <t>190</t>
+        </is>
+      </c>
+      <c r="B191">
+        <v>-0.9211727543591454</v>
+      </c>
+      <c r="C191">
+        <v>1.721806411762222</v>
+      </c>
+    </row>
+    <row r="192">
+      <c r="A192" t="inlineStr">
+        <is>
+          <t>191</t>
+        </is>
+      </c>
+      <c r="B192">
+        <v>-0.9606037666935353</v>
+      </c>
+      <c r="C192">
+        <v>0.1974954860843768</v>
+      </c>
+    </row>
+    <row r="193">
+      <c r="A193" t="inlineStr">
+        <is>
+          <t>192</t>
+        </is>
+      </c>
+      <c r="B193">
+        <v>-0.8783474235856883</v>
+      </c>
+      <c r="C193">
+        <v>-0.160927507784385</v>
+      </c>
+    </row>
+    <row r="194">
+      <c r="A194" t="inlineStr">
+        <is>
+          <t>193</t>
+        </is>
+      </c>
+      <c r="B194">
+        <v>1.549961673031378</v>
+      </c>
+      <c r="C194">
+        <v>-0.6781594125361454</v>
+      </c>
+    </row>
+    <row r="195">
+      <c r="A195" t="inlineStr">
+        <is>
+          <t>194</t>
+        </is>
+      </c>
+      <c r="B195">
+        <v>-0.7884053850501326</v>
+      </c>
+      <c r="C195">
+        <v>0.9691753767994852</v>
+      </c>
+    </row>
+    <row r="196">
+      <c r="A196" t="inlineStr">
+        <is>
+          <t>195</t>
+        </is>
+      </c>
+      <c r="B196">
+        <v>0.6298174131646814</v>
+      </c>
+      <c r="C196">
+        <v>-0.8622845572591453</v>
+      </c>
+    </row>
+    <row r="197">
+      <c r="A197" t="inlineStr">
+        <is>
+          <t>196</t>
+        </is>
+      </c>
+      <c r="B197">
+        <v>-0.5078207979005612</v>
+      </c>
+      <c r="C197">
+        <v>0.4788814309444154</v>
+      </c>
+    </row>
+    <row r="198">
+      <c r="A198" t="inlineStr">
+        <is>
+          <t>197</t>
+        </is>
+      </c>
+      <c r="B198">
+        <v>-0.6919621658263458</v>
+      </c>
+      <c r="C198">
+        <v>-0.7944957113876847</v>
+      </c>
+    </row>
+    <row r="199">
+      <c r="A199" t="inlineStr">
+        <is>
+          <t>198</t>
+        </is>
+      </c>
+      <c r="B199">
+        <v>0.190030134453737</v>
+      </c>
+      <c r="C199">
+        <v>-0.4582831983552963</v>
+      </c>
+    </row>
+    <row r="200">
+      <c r="A200" t="inlineStr">
+        <is>
+          <t>199</t>
+        </is>
+      </c>
+      <c r="B200">
+        <v>-1.44101027724417</v>
+      </c>
+      <c r="C200">
+        <v>1.084074081899838</v>
+      </c>
+    </row>
+    <row r="201">
+      <c r="A201" t="inlineStr">
+        <is>
+          <t>200</t>
+        </is>
+      </c>
+      <c r="B201">
+        <v>0.3790801005208568</v>
+      </c>
+      <c r="C201">
+        <v>-0.02396633292660763</v>
       </c>
     </row>
   </sheetData>
